--- a/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,298 +439,122 @@
           <t>dif_mean_last_180_matches_goal_ratio_against</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9749943906544315</v>
+        <v>0.621355385205324</v>
       </c>
       <c r="C2" t="n">
-        <v>0.690479929778097</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>0.4963988271494859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.1003256808284609</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>-0.5932057047728545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>IukqGdk1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4186310289445481</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.771417761132297</v>
-      </c>
-      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>Q5hiEzKD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5763531469738304</v>
+        <v>-0.3828639702651865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8376464513175979</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+        <v>0.7163648896698529</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>6uSGCr06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.112866359549527</v>
+        <v>-0.6370268378021041</v>
       </c>
       <c r="C6" t="n">
-        <v>1.27026289530676</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
+        <v>-1.776514047775256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.510669615138882</v>
+        <v>-0.1779167660970395</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.601120121705664</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.3600340479265446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>f18BYPMP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02582911048768314</v>
+        <v>0.9339492749802129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05235448814847767</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
+        <v>0.2652485426883799</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>SfGPAMUI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2150804327316325</v>
+        <v>-0.7067923825420074</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.345908399645439</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.8654323665893426</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8845498640787366</v>
+        <v>0.8113346756157077</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1640929164578384</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.621355385205324</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4963988271494859</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.1003256808284609</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.5932057047728545</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.1779167660970395</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.3600340479265446</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.7067923825420074</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.8654323665893426</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.3828639702651865</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.7163648896698529</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.9339492749802129</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.2652485426883799</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.6370268378021041</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.776514047775256</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.8113346756157077</v>
-      </c>
-      <c r="C19" t="n">
         <v>0.23312220132232</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,136 +425,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goal_ratio_against</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_goal_ratio_against</t>
+          <t>dif_mean_last_120_matches_goal_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.621355385205324</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.4963988271494859</v>
+        <v>-0.1729365025868828</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1003256808284609</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.5932057047728545</v>
+        <v>0.4860384074601836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IukqGdk1</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+        <v>-0.8364956026498997</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Q5hiEzKD</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3828639702651865</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.7163648896698529</v>
+        <v>-0.3768833460985067</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6uSGCr06</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.6370268378021041</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.776514047775256</v>
+        <v>1.210717202886448</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1779167660970395</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.3600340479265446</v>
+        <v>-1.022772859945979</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>f18BYPMP</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9339492749802129</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2652485426883799</v>
+        <v>-1.736089351899065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SfGPAMUI</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.7067923825420074</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.8654323665893426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8113346756157077</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.23312220132232</v>
+        <v>0.1951342487586736</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.680511358436192</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-1.179557554855823</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3526434699908486</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.916702409146755</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.074660221685341</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,151 +438,121 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1729365025868828</v>
+        <v>1.047496784531184</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4860384074601836</v>
+        <v>1.170565780670074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8364956026498997</v>
+        <v>-1.665907903404312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3768833460985067</v>
+        <v>1.210717202886448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.210717202886448</v>
+        <v>-0.9092653428564665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.022772859945979</v>
+        <v>0.4860384074601836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.736089351899065</v>
+        <v>-0.3768833460985067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0.1729365025868828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1951342487586736</v>
+        <v>-1.022772859945979</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.680511358436192</v>
+        <v>-1.736089351899065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.179557554855823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3526434699908486</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-1.916702409146755</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.074660221685341</v>
+        <v>0.1951342487586736</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,120 +425,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.047496784531184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.170565780670074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.665907903404312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>MiACepQ7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.210717202886448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rwXP4l3L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.9092653428564665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4860384074601836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3768833460985067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1729365025868828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.022772859945979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.736089351899065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -548,11 +548,71 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1951342487586736</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,193 +425,226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_sum_value_player_miss</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>-0.2601663087005531</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>-0.1383144710328494</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>-1.597783865194464</v>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-2.167289721400472</v>
+      </c>
+      <c r="C5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.02430268063542598</v>
+      </c>
+      <c r="C6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-0.4952084381675927</v>
+      </c>
+      <c r="C7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-1.430440262659445</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.04831677239572466</v>
+      </c>
+      <c r="C9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-1.391825598313292</v>
+      </c>
+      <c r="C10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-0.5818615409772313</v>
+      </c>
+      <c r="C11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-0.2695694000129745</v>
+      </c>
+      <c r="C12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2.127753043976391</v>
+      </c>
+      <c r="C13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-0.5094643309106239</v>
+      </c>
+      <c r="C14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fHjVr7t2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>z1eeWTdd</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+        <v>-0.8756402841692911</v>
+      </c>
+      <c r="C17" t="n">
         <v>0</v>
       </c>
     </row>
